--- a/UnityModules/Assets/Data/Editor/Excel/LinkGame.xlsx
+++ b/UnityModules/Assets/Data/Editor/Excel/LinkGame.xlsx
@@ -1000,24 +1000,24 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>7</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>8</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>8</v>
       </c>
     </row>
